--- a/survey_templates/049_thanksgiving_gratitude_notes--survey_templates.xlsx
+++ b/survey_templates/049_thanksgiving_gratitude_notes--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -761,8 +761,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,12 +790,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'word_of_mouth'}</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Word of mouth'}</t>
+          <t>Word of mouth</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'friends'}</t>
+          <t>friends</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'Friends'}</t>
+          <t>Friends</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'neighbors'}</t>
+          <t>neighbors</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'Neighbors'}</t>
+          <t>Neighbors</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'colleagues'}</t>
+          <t>colleagues</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'Colleagues'}</t>
+          <t>Colleagues</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_'strangers'}</t>
+          <t>strangers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 'Strangers'}</t>
+          <t>Strangers</t>
         </is>
       </c>
     </row>
